--- a/output/盛岡赤十字病院_随意契約_X線関連.xlsx
+++ b/output/盛岡赤十字病院_随意契約_X線関連.xlsx
@@ -850,7 +850,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>不明（令和6年5月23日〜令和6年12月9日）</t>
+          <t>不明（令和6年5月23日〜令和7年1月22日）</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14">
